--- a/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513261_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/playoffs/individual/NP_play_by_play_2513261_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.3749</v>
+        <v>9.7841</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9961</v>
+        <v>5.3476</v>
       </c>
       <c r="F2" t="n">
-        <v>4.3788</v>
+        <v>4.4365</v>
       </c>
       <c r="G2" t="n">
         <v>5.2612</v>
@@ -610,13 +610,13 @@
         <v>2.423</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3868</v>
+        <v>0.796</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.3079</v>
+        <v>0.0436</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6947</v>
+        <v>0.7523</v>
       </c>
       <c r="V2" t="n">
         <v>1.3039</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.8203</v>
+        <v>6.1878</v>
       </c>
       <c r="E3" t="n">
-        <v>2.0041</v>
+        <v>1.4292</v>
       </c>
       <c r="F3" t="n">
-        <v>4.8162</v>
+        <v>4.7586</v>
       </c>
       <c r="G3" t="n">
         <v>4.3717</v>
@@ -688,13 +688,13 @@
         <v>2.423</v>
       </c>
       <c r="S3" t="n">
-        <v>1.127</v>
+        <v>0.4945</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8216</v>
+        <v>0.2467</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3054</v>
+        <v>0.2477</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.9112</v>
+        <v>4.6574</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5296</v>
+        <v>1.881</v>
       </c>
       <c r="F4" t="n">
-        <v>3.3816</v>
+        <v>2.7763</v>
       </c>
       <c r="G4" t="n">
         <v>2.2173</v>
@@ -766,13 +766,13 @@
         <v>0.6608000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7292</v>
+        <v>0.4754</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3203</v>
+        <v>0.0312</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0495</v>
+        <v>0.4441</v>
       </c>
       <c r="V4" t="n">
         <v>1.3039</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MUNOZ BORCHERS</t>
+          <t>T. BORG</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.5028</v>
+        <v>4.615</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1341</v>
+        <v>1.1762</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3687</v>
+        <v>3.4388</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9161</v>
+        <v>2.8739</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1014</v>
+        <v>-1.2954</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8147</v>
+        <v>4.1693</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8466</v>
+        <v>0.8044</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4378</v>
+        <v>-1.4903</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5911999999999999</v>
+        <v>2.2947</v>
       </c>
       <c r="M5" t="n">
         <v>2.0695</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6635</v>
+        <v>0.1949</v>
       </c>
       <c r="O5" t="n">
-        <v>1.406</v>
+        <v>1.8746</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.3216</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1014</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1014</v>
+        <v>1.3216</v>
       </c>
       <c r="S5" t="n">
-        <v>1.5867</v>
+        <v>0.4195</v>
       </c>
       <c r="T5" t="n">
-        <v>1.27</v>
+        <v>0.3718</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3167</v>
+        <v>0.0477</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.1189</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1189</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. KUNKEL</t>
+          <t>V. VUCETIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.4232</v>
+        <v>4.4049</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4191</v>
+        <v>1.4282</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0041</v>
+        <v>2.9767</v>
       </c>
       <c r="G6" t="n">
-        <v>3.1074</v>
+        <v>2.1985</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2692</v>
+        <v>0.8488</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1618</v>
+        <v>1.3497</v>
       </c>
       <c r="J6" t="n">
-        <v>1.8933</v>
+        <v>-0.0272</v>
       </c>
       <c r="K6" t="n">
-        <v>3.2545</v>
+        <v>0.3415</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.3613</v>
+        <v>-0.3687</v>
       </c>
       <c r="M6" t="n">
-        <v>1.2141</v>
+        <v>2.2257</v>
       </c>
       <c r="N6" t="n">
-        <v>1.0146</v>
+        <v>0.5073</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1995</v>
+        <v>1.7184</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.2027</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.4054</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2027</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2807</v>
+        <v>0.6116</v>
       </c>
       <c r="T6" t="n">
-        <v>0.6935</v>
+        <v>0.1515</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5872000000000001</v>
+        <v>0.4602</v>
       </c>
       <c r="V6" t="n">
-        <v>2.2378</v>
+        <v>0.9339</v>
       </c>
       <c r="W6" t="n">
-        <v>2.2378</v>
+        <v>1.3039</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. VUCETIC</t>
+          <t>A. KUNKEL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>4.3491</v>
+        <v>4.0736</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5454</v>
+        <v>0.1848</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8037</v>
+        <v>3.8888</v>
       </c>
       <c r="G7" t="n">
-        <v>2.1985</v>
+        <v>3.1074</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8488</v>
+        <v>4.2692</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3497</v>
+        <v>-1.1618</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0272</v>
+        <v>1.8933</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3415</v>
+        <v>3.2545</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.3687</v>
+        <v>-1.3613</v>
       </c>
       <c r="M7" t="n">
-        <v>2.2257</v>
+        <v>1.2141</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5073</v>
+        <v>1.0146</v>
       </c>
       <c r="O7" t="n">
-        <v>1.7184</v>
+        <v>0.1995</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6608000000000001</v>
+        <v>-2.2027</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-4.4054</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6608000000000001</v>
+        <v>2.2027</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5558</v>
+        <v>0.9311</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2686</v>
+        <v>0.4592</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2872</v>
+        <v>0.4719</v>
       </c>
       <c r="V7" t="n">
-        <v>0.9339</v>
+        <v>2.2378</v>
       </c>
       <c r="W7" t="n">
-        <v>1.3039</v>
+        <v>2.2378</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. BORG</t>
+          <t>A. MUNOZ BORCHERS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.3273</v>
+        <v>3.9522</v>
       </c>
       <c r="E8" t="n">
-        <v>0.292</v>
+        <v>1.6124</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0353</v>
+        <v>2.3399</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8739</v>
+        <v>2.9161</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.2954</v>
+        <v>2.1014</v>
       </c>
       <c r="I8" t="n">
-        <v>4.1693</v>
+        <v>0.8147</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8044</v>
+        <v>0.8466</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4903</v>
+        <v>1.4378</v>
       </c>
       <c r="L8" t="n">
-        <v>2.2947</v>
+        <v>-0.5911999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>2.0695</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1949</v>
+        <v>0.6635</v>
       </c>
       <c r="O8" t="n">
-        <v>1.8746</v>
+        <v>1.406</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3216</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1014</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3216</v>
+        <v>1.1014</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8683</v>
+        <v>1.0362</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5124</v>
+        <v>0.7482</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3558</v>
+        <v>0.2879</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.1189</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="9">
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9004</v>
+        <v>1.9645</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.945</v>
+        <v>-0.881</v>
       </c>
       <c r="F9" t="n">
         <v>2.8455</v>
@@ -1156,10 +1156,10 @@
         <v>1.9825</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2843</v>
+        <v>0.3484</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1046</v>
+        <v>0.1686</v>
       </c>
       <c r="U9" t="n">
         <v>0.1797</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5508</v>
+        <v>0.7879</v>
       </c>
       <c r="E10" t="n">
-        <v>1.2988</v>
+        <v>1.3628</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7479</v>
+        <v>-0.575</v>
       </c>
       <c r="G10" t="n">
         <v>1.9669</v>
@@ -1234,13 +1234,13 @@
         <v>0.4405</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7377</v>
+        <v>-0.5007</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3843</v>
+        <v>-0.3203</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3534</v>
+        <v>-0.1804</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1189</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5371</v>
+        <v>0.6978</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.1178</v>
+        <v>-2.7554</v>
       </c>
       <c r="F11" t="n">
-        <v>3.6549</v>
+        <v>3.4532</v>
       </c>
       <c r="G11" t="n">
         <v>0.0415</v>
@@ -1312,13 +1312,13 @@
         <v>2.423</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4779</v>
+        <v>0.6385999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2157</v>
+        <v>0.1467</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6936</v>
+        <v>0.4919</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3039</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.4263</v>
+        <v>-0.3046</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6348</v>
+        <v>-0.5707</v>
       </c>
       <c r="F12" t="n">
-        <v>0.2084</v>
+        <v>0.2661</v>
       </c>
       <c r="G12" t="n">
         <v>1.3988</v>
@@ -1390,13 +1390,13 @@
         <v>0.4405</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6224</v>
+        <v>-0.5007</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1922</v>
+        <v>-0.1281</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.4302</v>
+        <v>-0.3726</v>
       </c>
       <c r="V12" t="n">
         <v>0.5595</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8088</v>
+        <v>-0.7178</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.6877</v>
+        <v>-3.7408</v>
       </c>
       <c r="F13" t="n">
-        <v>2.8789</v>
+        <v>3.023</v>
       </c>
       <c r="G13" t="n">
         <v>0.0684</v>
@@ -1468,13 +1468,13 @@
         <v>1.5419</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2164</v>
+        <v>-0.1253</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1797</v>
+        <v>-0.2329</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0366</v>
+        <v>0.1075</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>39.46200000000001</v>
+        <v>40.1028</v>
       </c>
       <c r="E14" t="n">
-        <v>5.833900000000002</v>
+        <v>6.474299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>33.6282</v>
+        <v>33.6284</v>
       </c>
       <c r="G14" t="n">
         <v>27.1567</v>
@@ -1546,19 +1546,19 @@
         <v>17.6217</v>
       </c>
       <c r="S14" t="n">
-        <v>3.9836</v>
+        <v>4.6246</v>
       </c>
       <c r="T14" t="n">
-        <v>1.0458</v>
+        <v>1.6862</v>
       </c>
       <c r="U14" t="n">
-        <v>2.938</v>
+        <v>2.9379</v>
       </c>
       <c r="V14" t="n">
         <v>3.9162</v>
       </c>
       <c r="W14" t="n">
-        <v>7.8279</v>
+        <v>7.827900000000001</v>
       </c>
       <c r="X14" t="n">
         <v>-3.9117</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6915</v>
+        <v>-0.7817</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1746</v>
+        <v>-0.4089</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5169</v>
+        <v>-0.3727</v>
       </c>
       <c r="G15" t="n">
         <v>-0.1654</v>
@@ -1624,13 +1624,13 @@
         <v>0.4405</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1523</v>
+        <v>0.0621</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5249</v>
+        <v>0.2905</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3726</v>
+        <v>-0.2284</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1189</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.4414</v>
+        <v>-0.784</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.3549</v>
+        <v>-2.6519</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9135</v>
+        <v>1.868</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8813</v>
@@ -1702,13 +1702,13 @@
         <v>1.3216</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5953000000000001</v>
+        <v>0.0621</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9608</v>
+        <v>-0.2579</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3655</v>
+        <v>0.32</v>
       </c>
       <c r="V16" t="n">
         <v>-0.185</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.944</v>
+        <v>-1.506</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.2122</v>
+        <v>-1.8607</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2682</v>
+        <v>0.3547</v>
       </c>
       <c r="G17" t="n">
         <v>-1.2127</v>
@@ -1780,13 +1780,13 @@
         <v>0.4405</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.07049999999999999</v>
+        <v>0.3675</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1922</v>
+        <v>0.1593</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1217</v>
+        <v>0.2082</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0677</v>
+        <v>-2.0119</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.8074</v>
+        <v>-1.9245</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2603</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="G18" t="n">
         <v>-1.2228</v>
@@ -1858,13 +1858,13 @@
         <v>0.4405</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.369</v>
+        <v>-0.3133</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0124</v>
+        <v>-0.1047</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3815</v>
+        <v>-0.2085</v>
       </c>
       <c r="V18" t="n">
         <v>0.185</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. LIMA BRITO</t>
+          <t>G. RENFROE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,40 +1891,40 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.2728</v>
+        <v>-2.7615</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0205</v>
+        <v>-1.9925</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2523</v>
+        <v>-0.769</v>
       </c>
       <c r="G19" t="n">
-        <v>-3.2601</v>
+        <v>-1.8201</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.5773</v>
+        <v>-0.094</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6828</v>
+        <v>-1.7261</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.8904</v>
+        <v>-0.8066</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.9284</v>
+        <v>-0.4216</v>
       </c>
       <c r="L19" t="n">
-        <v>0.038</v>
+        <v>-0.385</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3697</v>
+        <v>-1.0135</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3511</v>
+        <v>0.3276</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.7208</v>
+        <v>-1.3411</v>
       </c>
       <c r="P19" t="n">
         <v>0.2203</v>
@@ -1936,28 +1936,28 @@
         <v>1.3216</v>
       </c>
       <c r="S19" t="n">
-        <v>1.886</v>
+        <v>-0.4172</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9713</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.0854</v>
+        <v>-0.3327</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.1189</v>
+        <v>-0.7444</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1189</v>
+        <v>-0.7444</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. RENFROE</t>
+          <t>M. DIAZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4998</v>
+        <v>-3.6148</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.344</v>
+        <v>-3.8674</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1558</v>
+        <v>0.2526</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.8201</v>
+        <v>-3.1684</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.094</v>
+        <v>-3.3996</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7261</v>
+        <v>0.2312</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8066</v>
+        <v>-0.9787</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4216</v>
+        <v>-1.5704</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.385</v>
+        <v>0.5917</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0135</v>
+        <v>-2.1896</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3276</v>
+        <v>-1.8291</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3411</v>
+        <v>-0.3605</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2203</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1014</v>
+        <v>-2.2027</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3216</v>
+        <v>2.2027</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.1555</v>
+        <v>-0.4464</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.436</v>
+        <v>-0.6860000000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7195</v>
+        <v>0.2396</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.7444</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.7444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. KASIBABU SHILALA</t>
+          <t>A. LIMA BRITO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.3768</v>
+        <v>-4.1725</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.4068</v>
+        <v>-2.6607</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.97</v>
+        <v>-1.5118</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.9346</v>
+        <v>-3.2601</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.6824</v>
+        <v>-1.5773</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2521</v>
+        <v>-1.6828</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.4087</v>
+        <v>-1.8904</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.4087</v>
+        <v>-1.9284</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.038</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.5259</v>
+        <v>-1.3697</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2738</v>
+        <v>0.3511</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.2521</v>
+        <v>-1.7208</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.4405</v>
+        <v>0.2203</v>
       </c>
       <c r="Q21" t="n">
         <v>-1.1014</v>
       </c>
       <c r="R21" t="n">
-        <v>0.6608000000000001</v>
+        <v>1.3216</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2573</v>
+        <v>-0.0137</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8968</v>
+        <v>0.3311</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6395</v>
+        <v>-0.3448</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7444</v>
+        <v>-1.1189</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.7444</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. BELEMENE-DZABATOU</t>
+          <t>J. KASIBABU SHILALA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.4812</v>
+        <v>-4.4019</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.9226</v>
+        <v>-3.1725</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.5586</v>
+        <v>-1.2295</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.9961</v>
+        <v>-2.9346</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.182</v>
+        <v>-1.6824</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.814</v>
+        <v>-1.2521</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.9742</v>
+        <v>-1.4087</v>
       </c>
       <c r="K22" t="n">
-        <v>0.2171</v>
+        <v>-1.4087</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.1914</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.0218</v>
+        <v>-1.5259</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.3992</v>
+        <v>-0.2738</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3773</v>
+        <v>-1.2521</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6608000000000001</v>
+        <v>-0.4405</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.2027</v>
+        <v>-1.1014</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5419</v>
+        <v>0.6608000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>0.854</v>
+        <v>-0.2824</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2543</v>
+        <v>-0.6625</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4003</v>
+        <v>0.3801</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.6784</v>
+        <v>-0.7444</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.6784</v>
+        <v>-0.7444</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>M. DIAZ</t>
+          <t>D. MANCHON CRESPO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7985</v>
+        <v>-4.7089</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.0391</v>
+        <v>-3.7272</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2405</v>
+        <v>-0.9818</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1684</v>
+        <v>-3.0249</v>
       </c>
       <c r="H23" t="n">
-        <v>-3.3996</v>
+        <v>-1.0037</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2312</v>
+        <v>-2.0212</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.9787</v>
+        <v>-1.5325</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.5704</v>
+        <v>0.2628</v>
       </c>
       <c r="L23" t="n">
-        <v>0.5917</v>
+        <v>-1.7953</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.1896</v>
+        <v>-1.4924</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.8291</v>
+        <v>-1.2664</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.3605</v>
+        <v>-0.2259</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>-0.4405</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.2027</v>
       </c>
       <c r="R23" t="n">
-        <v>2.2027</v>
+        <v>1.7622</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.6301</v>
+        <v>-1.2435</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.8576</v>
+        <v>-1.1108</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2275</v>
+        <v>-0.1327</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.1189</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.1189</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. MANCHON CRESPO</t>
+          <t>J. BELEMENE-DZABATOU</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.2892</v>
+        <v>-5.5255</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.9615</v>
+        <v>-4.0943</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.3277</v>
+        <v>-1.4312</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.0249</v>
+        <v>-2.9961</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.0037</v>
+        <v>-1.182</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.0212</v>
+        <v>-1.814</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.5325</v>
+        <v>-1.9742</v>
       </c>
       <c r="K24" t="n">
-        <v>0.2628</v>
+        <v>0.2171</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.7953</v>
+        <v>-2.1914</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4924</v>
+        <v>-1.0218</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.2664</v>
+        <v>-1.3992</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.2259</v>
+        <v>0.3773</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4405</v>
+        <v>-0.6608000000000001</v>
       </c>
       <c r="Q24" t="n">
         <v>-2.2027</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7622</v>
+        <v>1.5419</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.8238</v>
+        <v>-0.1902</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.3452</v>
+        <v>0.0827</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4786</v>
+        <v>-0.2729</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.6784</v>
       </c>
       <c r="W24" t="n">
-        <v>1.1189</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1189</v>
+        <v>-1.6784</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-8.599299999999999</v>
+        <v>-8.4124</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.3848</v>
+        <v>-7.2676</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.2146</v>
+        <v>-1.1448</v>
       </c>
       <c r="G25" t="n">
         <v>-6.4702</v>
@@ -2404,13 +2404,13 @@
         <v>1.7622</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.9747</v>
+        <v>-0.7877999999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0125</v>
+        <v>-0.8953</v>
       </c>
       <c r="U25" t="n">
-        <v>0.0378</v>
+        <v>0.1075</v>
       </c>
       <c r="V25" t="n">
         <v>1.4889</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-39.4622</v>
+        <v>-38.6811</v>
       </c>
       <c r="E26" t="n">
-        <v>-33.62840000000001</v>
+        <v>-33.6282</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.834000000000001</v>
+        <v>-5.052899999999999</v>
       </c>
       <c r="G26" t="n">
         <v>-27.1566</v>
@@ -2467,7 +2467,7 @@
         <v>-10.1764</v>
       </c>
       <c r="N26" t="n">
-        <v>-6.9201</v>
+        <v>-6.920100000000001</v>
       </c>
       <c r="O26" t="n">
         <v>-3.2565</v>
@@ -2482,13 +2482,13 @@
         <v>13.2161</v>
       </c>
       <c r="S26" t="n">
-        <v>-3.9839</v>
+        <v>-3.2028</v>
       </c>
       <c r="T26" t="n">
-        <v>-2.9382</v>
+        <v>-2.9381</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.0459</v>
+        <v>-0.2646</v>
       </c>
       <c r="V26" t="n">
         <v>-3.916099999999999</v>
